--- a/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E53E29A-9DC9-4B29-9CCE-96285B67DA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7165B3A1-BB00-4BF1-A21A-1D89FB77B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" tabRatio="763" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10260" yWindow="1860" windowWidth="21585" windowHeight="10440" tabRatio="763" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
   <si>
     <t>Rate Sheet</t>
   </si>
@@ -310,13 +310,28 @@
   </si>
   <si>
     <t>Jason Chan</t>
+  </si>
+  <si>
+    <t>Roman Debald</t>
+  </si>
+  <si>
+    <t>Ayati Arvind</t>
+  </si>
+  <si>
+    <t>Bryan Loh</t>
+  </si>
+  <si>
+    <t>John Mavredakis</t>
+  </si>
+  <si>
+    <t>Jack Berka</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,12 +461,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="18">
@@ -706,8 +715,8 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1144,9 +1153,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1164,18 +1176,27 @@
       <c r="A2" t="s">
         <v>75</v>
       </c>
-      <c r="B2" t="s">
-        <v>90</v>
+      <c r="B2" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="C2" t="s">
         <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>76</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1183,15 +1204,24 @@
       <c r="A4" t="s">
         <v>77</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s">
         <v>87</v>
+      </c>
+      <c r="F4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>78</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1199,7 +1229,10 @@
       <c r="A6" t="s">
         <v>79</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1207,7 +1240,10 @@
       <c r="A7" t="s">
         <v>80</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1215,7 +1251,10 @@
       <c r="A8" t="s">
         <v>81</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1223,13 +1262,15 @@
       <c r="A9" t="s">
         <v>1</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
         <v>92</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7165B3A1-BB00-4BF1-A21A-1D89FB77B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0B539C-773B-47C1-ACD7-91CD0651C2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10260" yWindow="1860" windowWidth="21585" windowHeight="10440" tabRatio="763" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -21,10 +21,21 @@
     <sheet name="AddOpportunity" sheetId="19" r:id="rId6"/>
     <sheet name="AddContact" sheetId="21" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>

--- a/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0B539C-773B-47C1-ACD7-91CD0651C2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0D63F0-4800-43A9-8E83-A62E0E58A7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="763" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>

--- a/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0D63F0-4800-43A9-8E83-A62E0E58A7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255100C7-1002-439A-9264-30D1992DAF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="763" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
-    <sheet name="Update_Hours" sheetId="23" r:id="rId2"/>
-    <sheet name="DealTeamMembers" sheetId="25" r:id="rId3"/>
-    <sheet name="Update_Timer" sheetId="22" r:id="rId4"/>
-    <sheet name="RateSheetManagement" sheetId="17" r:id="rId5"/>
-    <sheet name="AddOpportunity" sheetId="19" r:id="rId6"/>
+    <sheet name="AddOpportunity" sheetId="19" r:id="rId2"/>
+    <sheet name="Update_Hours" sheetId="23" r:id="rId3"/>
+    <sheet name="DealTeamMembers" sheetId="25" r:id="rId4"/>
+    <sheet name="Update_Timer" sheetId="22" r:id="rId5"/>
+    <sheet name="RateSheetManagement" sheetId="17" r:id="rId6"/>
     <sheet name="AddContact" sheetId="21" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -200,9 +200,6 @@
     <t>CaoUser</t>
   </si>
   <si>
-    <t>Standard User</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -248,94 +245,97 @@
     <t>FVA</t>
   </si>
   <si>
+    <t>Time  Minutes</t>
+  </si>
+  <si>
+    <t>Weekly Time Entry</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>Staff Member</t>
+  </si>
+  <si>
+    <t>TAS - FY23 - DVC</t>
+  </si>
+  <si>
+    <t>10.0d</t>
+  </si>
+  <si>
+    <t>Senior Managing Director Rate</t>
+  </si>
+  <si>
+    <t>Managing Director Rate</t>
+  </si>
+  <si>
+    <t>Director Rate</t>
+  </si>
+  <si>
+    <t>Senior Vice President Rate</t>
+  </si>
+  <si>
+    <t>Vice President Rate</t>
+  </si>
+  <si>
+    <t>Associate Rate</t>
+  </si>
+  <si>
+    <t>Financial Analyst Rate</t>
+  </si>
+  <si>
+    <t>Brad Kay</t>
+  </si>
+  <si>
+    <t>Brett Ryan</t>
+  </si>
+  <si>
+    <t>Andrew Stacey</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Matthew White</t>
+  </si>
+  <si>
+    <t>Nancy Hoff</t>
+  </si>
+  <si>
+    <t>Drew Koecher</t>
+  </si>
+  <si>
+    <t>Alexander Drews</t>
+  </si>
+  <si>
+    <t>Sandy Ryan</t>
+  </si>
+  <si>
+    <t>Jason Chan</t>
+  </si>
+  <si>
+    <t>Roman Debald</t>
+  </si>
+  <si>
+    <t>Ayati Arvind</t>
+  </si>
+  <si>
+    <t>Bryan Loh</t>
+  </si>
+  <si>
+    <t>John Mavredakis</t>
+  </si>
+  <si>
+    <t>Jack Berka</t>
+  </si>
+  <si>
+    <t>StdUser</t>
+  </si>
+  <si>
+    <t>Coartney Trone</t>
+  </si>
+  <si>
     <t>Blaise Brunda</t>
-  </si>
-  <si>
-    <t>Time  Minutes</t>
-  </si>
-  <si>
-    <t>Weekly Time Entry</t>
-  </si>
-  <si>
-    <t>Hours</t>
-  </si>
-  <si>
-    <t>Staff Member</t>
-  </si>
-  <si>
-    <t>TAS - FY23 - DVC</t>
-  </si>
-  <si>
-    <t>10.0d</t>
-  </si>
-  <si>
-    <t>Senior Managing Director Rate</t>
-  </si>
-  <si>
-    <t>Managing Director Rate</t>
-  </si>
-  <si>
-    <t>Director Rate</t>
-  </si>
-  <si>
-    <t>Senior Vice President Rate</t>
-  </si>
-  <si>
-    <t>Vice President Rate</t>
-  </si>
-  <si>
-    <t>Associate Rate</t>
-  </si>
-  <si>
-    <t>Financial Analyst Rate</t>
-  </si>
-  <si>
-    <t>Brad Kay</t>
-  </si>
-  <si>
-    <t>Brett Ryan</t>
-  </si>
-  <si>
-    <t>Andrew Stacey</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Matthew White</t>
-  </si>
-  <si>
-    <t>Nancy Hoff</t>
-  </si>
-  <si>
-    <t>Drew Koecher</t>
-  </si>
-  <si>
-    <t>Alexander Drews</t>
-  </si>
-  <si>
-    <t>Sandy Ryan</t>
-  </si>
-  <si>
-    <t>Coartney Trone</t>
-  </si>
-  <si>
-    <t>Jason Chan</t>
-  </si>
-  <si>
-    <t>Roman Debald</t>
-  </si>
-  <si>
-    <t>Ayati Arvind</t>
-  </si>
-  <si>
-    <t>Bryan Loh</t>
-  </si>
-  <si>
-    <t>John Mavredakis</t>
-  </si>
-  <si>
-    <t>Jack Berka</t>
   </si>
 </sst>
 </file>
@@ -1051,27 +1051,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1080,222 +1082,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25574261-C7E9-4831-90EC-39FB8AD56B12}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{917D06E5-6D73-49DB-89C5-B5E08B0BD2AF}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15D6B4D-540D-4604-99A4-DF2B09749535}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{351367AD-7436-4842-8EB6-D7DC6164D492}">
   <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -1422,7 +1214,7 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
@@ -1488,7 +1280,7 @@
         <v>48</v>
       </c>
       <c r="Y2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Z2" t="s">
         <v>49</v>
@@ -1505,6 +1297,216 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25574261-C7E9-4831-90EC-39FB8AD56B12}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{917D06E5-6D73-49DB-89C5-B5E08B0BD2AF}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15D6B4D-540D-4604-99A4-DF2B09749535}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1523,28 +1525,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1552,25 +1554,25 @@
         <v>46</v>
       </c>
       <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/TMTT0013748_TMTT0013750_TMTT0013751_TMTT0013753_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -1,37 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E53E29A-9DC9-4B29-9CCE-96285B67DA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255100C7-1002-439A-9264-30D1992DAF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" tabRatio="763" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
-    <sheet name="Update_Hours" sheetId="23" r:id="rId2"/>
-    <sheet name="DealTeamMembers" sheetId="25" r:id="rId3"/>
-    <sheet name="Update_Timer" sheetId="22" r:id="rId4"/>
-    <sheet name="RateSheetManagement" sheetId="17" r:id="rId5"/>
-    <sheet name="AddOpportunity" sheetId="19" r:id="rId6"/>
+    <sheet name="AddOpportunity" sheetId="19" r:id="rId2"/>
+    <sheet name="Update_Hours" sheetId="23" r:id="rId3"/>
+    <sheet name="DealTeamMembers" sheetId="25" r:id="rId4"/>
+    <sheet name="Update_Timer" sheetId="22" r:id="rId5"/>
+    <sheet name="RateSheetManagement" sheetId="17" r:id="rId6"/>
     <sheet name="AddContact" sheetId="21" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
   <si>
     <t>Rate Sheet</t>
   </si>
@@ -189,9 +200,6 @@
     <t>CaoUser</t>
   </si>
   <si>
-    <t>Standard User</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -237,86 +245,104 @@
     <t>FVA</t>
   </si>
   <si>
+    <t>Time  Minutes</t>
+  </si>
+  <si>
+    <t>Weekly Time Entry</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>Staff Member</t>
+  </si>
+  <si>
+    <t>TAS - FY23 - DVC</t>
+  </si>
+  <si>
+    <t>10.0d</t>
+  </si>
+  <si>
+    <t>Senior Managing Director Rate</t>
+  </si>
+  <si>
+    <t>Managing Director Rate</t>
+  </si>
+  <si>
+    <t>Director Rate</t>
+  </si>
+  <si>
+    <t>Senior Vice President Rate</t>
+  </si>
+  <si>
+    <t>Vice President Rate</t>
+  </si>
+  <si>
+    <t>Associate Rate</t>
+  </si>
+  <si>
+    <t>Financial Analyst Rate</t>
+  </si>
+  <si>
+    <t>Brad Kay</t>
+  </si>
+  <si>
+    <t>Brett Ryan</t>
+  </si>
+  <si>
+    <t>Andrew Stacey</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Matthew White</t>
+  </si>
+  <si>
+    <t>Nancy Hoff</t>
+  </si>
+  <si>
+    <t>Drew Koecher</t>
+  </si>
+  <si>
+    <t>Alexander Drews</t>
+  </si>
+  <si>
+    <t>Sandy Ryan</t>
+  </si>
+  <si>
+    <t>Jason Chan</t>
+  </si>
+  <si>
+    <t>Roman Debald</t>
+  </si>
+  <si>
+    <t>Ayati Arvind</t>
+  </si>
+  <si>
+    <t>Bryan Loh</t>
+  </si>
+  <si>
+    <t>John Mavredakis</t>
+  </si>
+  <si>
+    <t>Jack Berka</t>
+  </si>
+  <si>
+    <t>StdUser</t>
+  </si>
+  <si>
+    <t>Coartney Trone</t>
+  </si>
+  <si>
     <t>Blaise Brunda</t>
-  </si>
-  <si>
-    <t>Time  Minutes</t>
-  </si>
-  <si>
-    <t>Weekly Time Entry</t>
-  </si>
-  <si>
-    <t>Hours</t>
-  </si>
-  <si>
-    <t>Staff Member</t>
-  </si>
-  <si>
-    <t>TAS - FY23 - DVC</t>
-  </si>
-  <si>
-    <t>10.0d</t>
-  </si>
-  <si>
-    <t>Senior Managing Director Rate</t>
-  </si>
-  <si>
-    <t>Managing Director Rate</t>
-  </si>
-  <si>
-    <t>Director Rate</t>
-  </si>
-  <si>
-    <t>Senior Vice President Rate</t>
-  </si>
-  <si>
-    <t>Vice President Rate</t>
-  </si>
-  <si>
-    <t>Associate Rate</t>
-  </si>
-  <si>
-    <t>Financial Analyst Rate</t>
-  </si>
-  <si>
-    <t>Brad Kay</t>
-  </si>
-  <si>
-    <t>Brett Ryan</t>
-  </si>
-  <si>
-    <t>Andrew Stacey</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Matthew White</t>
-  </si>
-  <si>
-    <t>Nancy Hoff</t>
-  </si>
-  <si>
-    <t>Drew Koecher</t>
-  </si>
-  <si>
-    <t>Alexander Drews</t>
-  </si>
-  <si>
-    <t>Sandy Ryan</t>
-  </si>
-  <si>
-    <t>Coartney Trone</t>
-  </si>
-  <si>
-    <t>Jason Chan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,12 +472,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="18">
@@ -706,8 +726,8 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1031,27 +1051,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1060,190 +1082,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25574261-C7E9-4831-90EC-39FB8AD56B12}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{917D06E5-6D73-49DB-89C5-B5E08B0BD2AF}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15D6B4D-540D-4604-99A4-DF2B09749535}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{351367AD-7436-4842-8EB6-D7DC6164D492}">
   <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -1370,7 +1214,7 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
         <v>35</v>
@@ -1436,7 +1280,7 @@
         <v>48</v>
       </c>
       <c r="Y2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Z2" t="s">
         <v>49</v>
@@ -1453,6 +1297,216 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25574261-C7E9-4831-90EC-39FB8AD56B12}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{917D06E5-6D73-49DB-89C5-B5E08B0BD2AF}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15D6B4D-540D-4604-99A4-DF2B09749535}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1471,28 +1525,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1500,25 +1554,25 @@
         <v>46</v>
       </c>
       <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
